--- a/reports/pdf_change_20261007.xlsx
+++ b/reports/pdf_change_20261007.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,293억   ·   현금 3억(0.0%)      당일 2026-10-07  vs  전영업일 2026-10-06      매수 3종목  /  매도 15종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,416억      당일 2026-10-07  vs  전영업일 2026-10-06      매수 3종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>125</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1923188368</v>
+        <v>1921215828</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-31</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-484506969</v>
+        <v>-484010029</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>64</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>5422562447</v>
+        <v>5417000736</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-28</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-312312141</v>
+        <v>-311991815</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>549120248</v>
+        <v>548557037</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-14</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-501637726</v>
+        <v>-501123216</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>-13</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-86063289</v>
+        <v>-85975017</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1008150455</v>
+        <v>-1038187048</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.81%</t>
+          <t>0.72%→0.54%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>42→31</t>
         </is>
       </c>
     </row>
@@ -856,23 +856,23 @@
       <c r="E11" s="17" t="n"/>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1039252969</v>
+        <v>-1007116434</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.54%</t>
+          <t>1.03%→0.81%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>42→31</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         <v>-9</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-736222832</v>
+        <v>-735467717</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>-7</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-204067592</v>
+        <v>-203858288</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>-6</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-138645063</v>
+        <v>-138502860</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-558090252</v>
+        <v>-137626259</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.43%</t>
+          <t>0.42%→0.38%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -996,23 +996,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-137767562</v>
+        <v>-557517840</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.38%</t>
+          <t>0.51%→0.43%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
         <v>-5</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-259350117</v>
+        <v>-259084112</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>-4</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-114075051</v>
+        <v>-113958049</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-4</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-768300347</v>
+        <v>-767512331</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>-3</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-895050404</v>
+        <v>-894132386</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,381억   ·   현금 27억(0.8%)      당일 2026-10-07  vs  전영업일 2026-10-06      매수 6종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,499억      당일 2026-10-07  vs  전영업일 2026-10-06      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1227,7 +1227,7 @@
         <v>72</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1084493132</v>
+        <v>1090713807</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>-176</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1613601934</v>
+        <v>-1622857589</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>63</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1446461543</v>
+        <v>1454758477</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>-122</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1022810493</v>
+        <v>-1028677356</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>17</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>348082756</v>
+        <v>350079367</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>-16</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1025917114</v>
+        <v>-1031801796</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>13</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>324992299</v>
+        <v>326856462</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>-10</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-666825204</v>
+        <v>-670650128</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>329490101</v>
+        <v>331380063</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>4</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>323423299</v>
+        <v>325278462</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,842억   ·   현금 43억(1.4%)      당일 2026-10-07  vs  전영업일 2026-10-06      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,947억      당일 2026-10-07  vs  전영업일 2026-10-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1476,7 +1476,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,093억   ·   현금 9억(0.4%)      당일 2026-10-07  vs  전영업일 2026-10-06      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,198억      당일 2026-10-07  vs  전영업일 2026-10-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1500,7 +1500,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 316억   ·   현금 2억(0.6%)      당일 2026-10-07  vs  전영업일 2026-10-06      매수 1종목  /  매도 1종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 325억      당일 2026-10-07  vs  전영업일 2026-10-06      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -1596,11 +1596,11 @@
         <v>16</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>40364788</v>
+        <v>39984000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>1.14%→1.27%</t>
+          <t>1.10%→1.22%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1617,11 +1617,11 @@
         <v>-34</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-25755672</v>
+        <v>-27928960</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>1.61%→1.53%</t>
+          <t>1.70%→1.61%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">

--- a/reports/pdf_change_20261007.xlsx
+++ b/reports/pdf_change_20261007.xlsx
@@ -828,23 +828,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1038187048</v>
+        <v>-1007116434</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.54%</t>
+          <t>1.03%→0.81%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>42→31</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -856,23 +856,23 @@
       <c r="E11" s="17" t="n"/>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1007116434</v>
+        <v>-1038187048</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.81%</t>
+          <t>0.72%→0.54%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>42→31</t>
         </is>
       </c>
     </row>
@@ -940,23 +940,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-138502860</v>
+        <v>-557517840</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.41%</t>
+          <t>0.51%→0.43%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>102→96</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -996,23 +996,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-557517840</v>
+        <v>-138502860</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.43%</t>
+          <t>0.45%→0.41%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>102→96</t>
         </is>
       </c>
     </row>
@@ -1052,23 +1052,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-113958049</v>
+        <v>-767512331</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.02%→0.00%</t>
+          <t>6.79%→6.59%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>4→0</t>
+          <t>190→186</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-767512331</v>
+        <v>-113958049</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>6.79%→6.59%</t>
+          <t>0.02%→0.00%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>190→186</t>
+          <t>4→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261007.xlsx
+++ b/reports/pdf_change_20261007.xlsx
@@ -940,23 +940,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-557517840</v>
+        <v>-137626259</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.43%</t>
+          <t>0.42%→0.38%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -968,23 +968,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-137626259</v>
+        <v>-557517840</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.38%</t>
+          <t>0.51%→0.43%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1052,23 +1052,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-767512331</v>
+        <v>-113958049</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>6.79%→6.59%</t>
+          <t>0.02%→0.00%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>190→186</t>
+          <t>4→0</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-113958049</v>
+        <v>-767512331</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.02%→0.00%</t>
+          <t>6.79%→6.59%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>4→0</t>
+          <t>190→186</t>
         </is>
       </c>
     </row>
